--- a/data/Demersales/spp_pars_wiki.xlsx
+++ b/data/Demersales/spp_pars_wiki.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\apaz\Documents\hake-mizer\data\Demersales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2E3394-B0B4-4DA3-AF33-05A882FD6391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABD4C81-9E12-440E-A37C-3749D833D12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{989B7B2A-5335-4516-8F59-C702E446D0B0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>esp</t>
   </si>
@@ -111,6 +111,24 @@
   </si>
   <si>
     <t>al0</t>
+  </si>
+  <si>
+    <t>Lep_bosc</t>
+  </si>
+  <si>
+    <t>Lepidorhombus boscii</t>
+  </si>
+  <si>
+    <t>Four-spot megrim</t>
+  </si>
+  <si>
+    <t>Lep_whif</t>
+  </si>
+  <si>
+    <t>Lepidorhombus whiffiagonis</t>
+  </si>
+  <si>
+    <t>Megrim</t>
   </si>
 </sst>
 </file>
@@ -462,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3220922-D13B-4CCC-88AA-A4C380158BE2}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
@@ -529,121 +547,176 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>3.8E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="E3">
-        <v>3.1320000000000001</v>
+        <v>3.1777000000000002</v>
       </c>
       <c r="F3">
-        <f>(63.93+57.43)/2</f>
-        <v>60.68</v>
+        <v>37.1</v>
       </c>
       <c r="G3">
-        <f>(0.18+0.21)/2</f>
-        <v>0.19500000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H3">
-        <f>(-1.41-1.39)/2</f>
-        <v>-1.4</v>
+        <v>-0.47</v>
       </c>
       <c r="I3">
-        <v>35.25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>1.0776000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E4">
-        <v>2.9122699999999999</v>
+        <v>3.0964999999999998</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="H4">
-        <v>-0.96</v>
+        <v>-0.59</v>
       </c>
       <c r="I4">
-        <v>14.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>5.3E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="E5">
-        <v>3.0840000000000001</v>
+        <v>3.1320000000000001</v>
       </c>
       <c r="F5">
-        <v>42.7</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="G5">
-        <v>0.26800000000000002</v>
+        <v>0.36</v>
       </c>
       <c r="H5">
-        <v>-2.17</v>
+        <v>-1.07</v>
       </c>
       <c r="I5">
-        <v>28.7</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>1.0776000000000001E-2</v>
+      </c>
+      <c r="E6">
+        <v>2.9122699999999999</v>
+      </c>
+      <c r="F6">
+        <v>20.7</v>
+      </c>
+      <c r="G6">
+        <v>0.69</v>
+      </c>
+      <c r="H6">
+        <v>-0.64</v>
+      </c>
+      <c r="I6">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>5.3E-3</v>
+      </c>
+      <c r="E7">
+        <v>3.0840000000000001</v>
+      </c>
+      <c r="F7">
+        <v>37.4</v>
+      </c>
+      <c r="G7">
+        <v>0.47</v>
+      </c>
+      <c r="H7">
+        <v>-0.97</v>
+      </c>
+      <c r="I7">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D6">
+      <c r="D8">
         <v>1.291E-2</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <v>2.8544999999999998</v>
       </c>
-      <c r="F6">
-        <v>30.9</v>
-      </c>
-      <c r="G6">
-        <v>0.24</v>
-      </c>
-      <c r="H6">
-        <v>-1.82</v>
-      </c>
-      <c r="I6">
-        <v>22.9</v>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8">
+        <v>0.25</v>
+      </c>
+      <c r="H8">
+        <v>-0.98</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
